--- a/public/files/event/event.xlsx
+++ b/public/files/event/event.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\event\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A4CCDE-42AC-4980-96CB-C01EE53B91B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C042C94-DCAE-4F7E-AD49-040ACABFF2D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1320" yWindow="420" windowWidth="26205" windowHeight="14850" firstSheet="8" activeTab="16" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
+    <workbookView xWindow="210" yWindow="525" windowWidth="26205" windowHeight="14850" firstSheet="8" activeTab="12" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
   </bookViews>
   <sheets>
     <sheet name="1207event" sheetId="3" r:id="rId1"/>
@@ -31,6 +31,8 @@
     <sheet name="Sheet2" sheetId="18" r:id="rId16"/>
     <sheet name="塔21F" sheetId="19" r:id="rId17"/>
     <sheet name="塔21Fb" sheetId="20" r:id="rId18"/>
+    <sheet name="塔崩壊" sheetId="21" r:id="rId19"/>
+    <sheet name="Sheet5" sheetId="22" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="440">
   <si>
     <t>今日は12月14日。</t>
     <rPh sb="0" eb="2">
@@ -2551,6 +2553,114 @@
   <si>
     <t>紫苑は冷たい空気を肺に吸い込み、やれやれと小さく息をついた。どうやら、この悪魔とは、まだ長い付き合いになりそうだ。</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紫苑は、小さく息を吐いた。</t>
+  </si>
+  <si>
+    <t>その一言が、口からこぼれ落ちた瞬間だった。</t>
+  </si>
+  <si>
+    <t>——ビル全体が、大きく跳ねた。</t>
+  </si>
+  <si>
+    <t>何が起きたのか、理解する時間さえ与えられなかった。</t>
+  </si>
+  <si>
+    <t>声を上げる暇もなかった。悲鳴すら、形を成す前に消えた。</t>
+  </si>
+  <si>
+    <t>熱、と認識するよりも早く、それは熱の域を超えていた。</t>
+  </si>
+  <si>
+    <t>肌が、髪が、服が——輪郭を保っていられる時間は、まばたき一つ分にも満たなかった。</t>
+  </si>
+  <si>
+    <t>痛みを感じる神経が仕事をする前に、それを伝えるはずの体そのものが、存在しなくなった。</t>
+  </si>
+  <si>
+    <t>骨も、肉も、涙の一粒すら、残らなかった。</t>
+  </si>
+  <si>
+    <t>それを見た者がいたとすれば、の話だが。</t>
+  </si>
+  <si>
+    <t>何もかもが消え失せた、その静寂の中心で——</t>
+  </si>
+  <si>
+    <t>瓦礫の隙間から差し込む光が、少しずつ色を変えていくのが分かった。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>夜通し続いた緊張から解放され、紫苑は壁にもたれたまま、しばらくぼんやりとその変化を眺めていた。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>体の芯に残る疲労が、まだ完全には抜けきっていない。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>それでも、朝が近いという事実だけが、かすかな安堵を連れてくる。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「……夜が明けてきた……」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>床が、壁が、天井が、同時に軋む。今まで感じたことのない振動が、</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>下から突き上げるように全身を貫いた。反射的に立ち上がろうとした体が、その勢いのまま崩れる。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>視界の端で、空気そのものが歪むのが見えた気がした。歪みは光を帯び、</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>光は瞬く間に白へと変わっていく。まるで太陽そのものが、すぐ真横に生まれたかのようだった。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プラズマの膜に閉じ込められた灼熱の球が、ビルを、瓦礫を、緑に覆われた街の一角を、まとめて塗り潰す。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>爆心地には、後に何かがあったと示すものすら残らない。ただ、更地よりもなお平らな、何もない場所が広がるだけだった。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>夜明け前の空に、太陽が二つ昇ったように見えたかもしれない。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リフィエル「私も突然迷い込んでしまってわからないのです…」</t>
+  </si>
+  <si>
+    <t>紫苑｢そうか…｣</t>
+  </si>
+  <si>
+    <t>紫苑は力なくうなだれた。</t>
+  </si>
+  <si>
+    <t>紫苑｢ちょっと疲れちゃった、リフィ…エル?さんは何か…魔法とか使えたりするの？｣</t>
+  </si>
+  <si>
+    <t>リフィエル「私には力はありませんが、ほんの少しだけ異次元の力、ごくわずかに世界の法則を変える力をお借りすることができます。」</t>
+  </si>
+  <si>
+    <t>紫苑「…」</t>
+  </si>
+  <si>
+    <t>リフィエル「それは私自身には大した力を発揮しませんが、紫苑さんのようなかたであればその少しの変化でも大きな力にすることができるかもしれません。」</t>
+  </si>
+  <si>
+    <t>紫苑「そうか…それじゃあこの先どうなるかわからないけど一緒に来てくれるかい？」</t>
+  </si>
+  <si>
+    <t>リフィエル「ぜひお願いします！」</t>
   </si>
 </sst>
 </file>
@@ -4104,6 +4214,132 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF533422-054A-4996-9422-7AADF2D8C669}">
+  <dimension ref="A1:A23"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>418</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{297D6DA5-2661-4E45-AB92-D2EA5AC3D0F2}">
   <dimension ref="A1:A53"/>
@@ -4372,6 +4608,62 @@
     <row r="53" spans="1:1">
       <c r="A53" t="s">
         <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{364D305E-18B4-4FC4-B464-200B9DF83594}">
+  <dimension ref="A1:A10"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>439</v>
       </c>
     </row>
   </sheetData>
